--- a/OUTPUT/reverse_Q8EHJ3_Shewanella_oneidensis_MR-1.xlsx
+++ b/OUTPUT/reverse_Q8EHJ3_Shewanella_oneidensis_MR-1.xlsx
@@ -482,11 +482,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9822071171531388</v>
       </c>
     </row>
     <row r="3">
@@ -511,11 +511,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9822071171531388</v>
       </c>
     </row>
   </sheetData>
